--- a/daily_matches/job_matches_2026-10-11.xlsx
+++ b/daily_matches/job_matches_2026-10-11.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,140 +456,105 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer AI</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Karoo Health</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FL, USA USA</t>
+          <t>Pittsburgh, PA, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, S3, Athena, Redshift, BigQuery, Data Lake, Apache Airflow, CI/CD, Git, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a34cbe3d8382805b</t>
+          <t>https://www.indeed.com/viewjob?jk=89a4ee98072606c4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer AI</t>
+          <t>Solutions Engineer - Splunk (Remote)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MA, USA USA</t>
+          <t>San Jose, CA, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7450ea7e0a46fadb</t>
+          <t>https://www.indeed.com/viewjob?jk=0557188a83024668</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Solutions Engineer - Splunk (Remote)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Prompt Engineering, BigQuery, Dataflow, Docker, CI/CD, Git</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0ecd01a06f53156</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist - AI Engineer (Healthcare)</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>American Radiologist Network</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Remote, USA USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Hugging Face, TensorFlow, PyTorch, YOLO, Docker, Kubernetes, Python, R</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=87aad3290cc5e7a9</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc8f9acd90796dc</t>
         </is>
       </c>
     </row>
